--- a/WorkBot/main/data/order_archive/Ithaca Bakery/Ithaca Bakery_Triphammer_20260724.xlsx
+++ b/WorkBot/main/data/order_archive/Ithaca Bakery/Ithaca Bakery_Triphammer_20260724.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,41 +902,41 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Casa/RH</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
+          <t>Diannes - Cheesecake Irish Cream</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>85.84999999999999</v>
+        <v>59.73</v>
       </c>
       <c r="E28" t="n">
-        <v>257.55</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Grandma's</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diannes - Cheesecake Irish Cream</t>
+          <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>59.73</v>
+        <v>18.35</v>
       </c>
       <c r="E29" t="n">
-        <v>59.73</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="30">
@@ -947,7 +947,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Apple</t>
+          <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -984,64 +984,212 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grandma's</t>
+          <t>DV 053115</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
+          <t>DV - Gummi Bears (12 oz)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>18.35</v>
+        <v>2.83</v>
       </c>
       <c r="E32" t="n">
-        <v>18.35</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DV 053115</t>
+          <t>DV 053440</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DV - Gummi Bears (12 oz)</t>
+          <t>DV - Dried Pineapple Tidbit</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="E33" t="n">
-        <v>33.96</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>DV 053440</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DV - Dried Pineapple Tidbit</t>
+          <t>Flour - Rice</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>3.04</v>
+        <v>35.57</v>
       </c>
       <c r="E34" t="n">
-        <v>36.48</v>
+        <v>35.57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Lentz</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="E35" t="n">
+        <v>43.94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Butter - Unsalted</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Goat Cheese</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>22.24</v>
+      </c>
+      <c r="E37" t="n">
+        <v>155.68</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PERF</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Egg Patty - Vegan</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="E38" t="n">
+        <v>99.59</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Casa/RH</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Smoked Salmon (Sliced)</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>257.55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H&amp;M/JP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Scrubbies - Steel</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Floor Cleaner - Lucky 7</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12.55</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mop Head Cut (White)</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
